--- a/data_raw/data_raw_2024_sheets/LTER1_BR_T03_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER1_BR_T03_2024.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Documents/Work/Coral reefs/Demography study/Coral data/Demographic transect data/Data files/2024/Data 2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D405919-A8D0-064C-997E-12D954435162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFCE091-CFF9-814C-A4D1-205B0C192281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="500" windowWidth="35580" windowHeight="22920" xr2:uid="{4273570F-2639-FB44-8A16-45407BEB9269}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="18780" xr2:uid="{4273570F-2639-FB44-8A16-45407BEB9269}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="28">
   <si>
     <t>LTER1</t>
   </si>
@@ -186,367 +186,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFA500"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -1084,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924AF811-60F3-8042-BEA4-D19A3635F83B}">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1777,22 +1417,31 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>2.5299999999999998</v>
+        <v>2.78</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="I21" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="J21" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="K21" s="5">
+        <v>2.7</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -1809,28 +1458,19 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="J22" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="K22" s="5">
-        <v>2.7</v>
-      </c>
       <c r="L22" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -1844,19 +1484,19 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G23">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
@@ -1873,22 +1513,31 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24">
         <v>3</v>
       </c>
-      <c r="E24">
-        <v>3.15</v>
-      </c>
       <c r="F24">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="I24" s="5">
+        <v>22.1</v>
+      </c>
+      <c r="J24" s="5">
+        <v>15.5</v>
+      </c>
+      <c r="K24" s="5">
+        <v>15.5</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -1902,31 +1551,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="5">
-        <v>22.1</v>
-      </c>
-      <c r="J25" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="K25" s="5">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="L25" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1940,22 +1580,31 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="F26">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G26">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>6</v>
+        <v>24</v>
+      </c>
+      <c r="I26" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="J26" s="5">
+        <v>14</v>
+      </c>
+      <c r="K26" s="5">
+        <v>6.8</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -1969,31 +1618,22 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="F27">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G27">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="5">
-        <v>14.8</v>
-      </c>
-      <c r="J27" s="5">
-        <v>14</v>
-      </c>
-      <c r="K27" s="5">
-        <v>6.8</v>
-      </c>
       <c r="L27" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -2007,22 +1647,31 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="F28">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="I28" s="5">
+        <v>6.8</v>
+      </c>
+      <c r="J28" s="5">
+        <v>6.5</v>
+      </c>
+      <c r="K28" s="5">
+        <v>6.8</v>
       </c>
       <c r="L28" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -2042,22 +1691,22 @@
         <v>3.4</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I29" s="5">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="J29" s="5">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="K29" s="5">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="s">
         <v>4</v>
@@ -2077,28 +1726,19 @@
         <v>5</v>
       </c>
       <c r="E30">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="H30" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="J30" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="K30" s="5">
-        <v>3.5</v>
-      </c>
       <c r="L30" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -2115,16 +1755,16 @@
         <v>5</v>
       </c>
       <c r="E31">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="F31">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G31">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L31" t="s">
         <v>25</v>
@@ -2144,16 +1784,16 @@
         <v>5</v>
       </c>
       <c r="E32">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="F32">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G32">
         <v>50</v>
       </c>
       <c r="H32" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L32" t="s">
         <v>25</v>
@@ -2173,13 +1813,13 @@
         <v>5</v>
       </c>
       <c r="E33">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="F33">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G33">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
         <v>24</v>
@@ -2205,10 +1845,10 @@
         <v>3.86</v>
       </c>
       <c r="F34">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G34">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H34" t="s">
         <v>24</v>
@@ -2234,7 +1874,7 @@
         <v>3.86</v>
       </c>
       <c r="F35">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G35">
         <v>37</v>
@@ -2257,22 +1897,31 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="F36">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="G36">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="I36" s="5">
+        <v>11.8</v>
+      </c>
+      <c r="J36" s="5">
+        <v>12</v>
+      </c>
+      <c r="K36" s="5">
+        <v>7.5</v>
       </c>
       <c r="L36" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -2289,13 +1938,13 @@
         <v>5</v>
       </c>
       <c r="E37">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="F37">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G37">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="H37" t="s">
         <v>24</v>
@@ -2315,31 +1964,22 @@
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>3.95</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="G38">
         <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>4</v>
-      </c>
-      <c r="I38" s="5">
-        <v>11.8</v>
-      </c>
-      <c r="J38" s="5">
-        <v>12</v>
-      </c>
-      <c r="K38" s="5">
-        <v>7.5</v>
+        <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -2353,22 +1993,31 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="F39">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="I39" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="J39" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="K39" s="5">
+        <v>2</v>
       </c>
       <c r="L39" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -2382,22 +2031,31 @@
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>3.95</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F40">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="I40" s="5">
+        <v>7.2</v>
+      </c>
+      <c r="J40" s="5">
+        <v>6.8</v>
+      </c>
+      <c r="K40" s="5">
+        <v>6</v>
       </c>
       <c r="L40" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -2411,28 +2069,28 @@
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>4.04</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G41">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H41" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I41" s="5">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="J41" s="5">
-        <v>3.5</v>
+        <v>29</v>
       </c>
       <c r="K41" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L41" t="s">
         <v>4</v>
@@ -2452,28 +2110,19 @@
         <v>7</v>
       </c>
       <c r="E42">
-        <v>4.0999999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" s="5">
-        <v>7.2</v>
-      </c>
-      <c r="J42" s="5">
-        <v>6.8</v>
-      </c>
-      <c r="K42" s="5">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L42" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -2487,28 +2136,25 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>4.5999999999999996</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="F43">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="G43">
-        <v>37</v>
-      </c>
-      <c r="H43" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="I43" s="5">
-        <v>25.5</v>
+        <v>3.5</v>
       </c>
       <c r="J43" s="5">
-        <v>29</v>
+        <v>3.5</v>
       </c>
       <c r="K43" s="5">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="L43" t="s">
         <v>4</v>
@@ -2525,22 +2171,28 @@
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44" t="s">
-        <v>24</v>
+        <v>55</v>
+      </c>
+      <c r="I44" s="5">
+        <v>12</v>
+      </c>
+      <c r="J44" s="5">
+        <v>9</v>
+      </c>
+      <c r="K44" s="5">
+        <v>17</v>
       </c>
       <c r="L44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
@@ -2557,25 +2209,25 @@
         <v>7</v>
       </c>
       <c r="E45">
-        <v>4.3499999999999996</v>
+        <v>2.09</v>
       </c>
       <c r="F45">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="G45">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I45" s="5">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="J45" s="5">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="K45" s="5">
-        <v>2.7</v>
+        <v>0.25</v>
       </c>
       <c r="L45" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -2592,25 +2244,25 @@
         <v>5</v>
       </c>
       <c r="E46">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="F46">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="I46" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J46" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K46" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -2627,22 +2279,22 @@
         <v>7</v>
       </c>
       <c r="E47">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="F47">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G47">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="I47" s="5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J47" s="5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K47" s="5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L47" t="s">
         <v>23</v>
@@ -2659,25 +2311,25 @@
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E48">
-        <v>3.9</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="F48">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I48" s="5">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J48" s="5">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="K48" s="5">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="L48" t="s">
         <v>23</v>
@@ -2697,13 +2349,13 @@
         <v>7</v>
       </c>
       <c r="E49">
-        <v>3.05</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="F49">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="I49" s="5">
         <v>1</v>
@@ -2732,22 +2384,22 @@
         <v>7</v>
       </c>
       <c r="E50">
-        <v>4.6500000000000004</v>
+        <v>1.2</v>
       </c>
       <c r="F50">
         <v>30</v>
       </c>
       <c r="G50">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I50" s="5">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J50" s="5">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="K50" s="5">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="L50" t="s">
         <v>23</v>
@@ -2767,13 +2419,13 @@
         <v>7</v>
       </c>
       <c r="E51">
-        <v>4.8499999999999996</v>
+        <v>1.4</v>
       </c>
       <c r="F51">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G51">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="I51" s="5">
         <v>1</v>
@@ -2802,7 +2454,7 @@
         <v>7</v>
       </c>
       <c r="E52">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="F52">
         <v>30</v>
@@ -2837,13 +2489,13 @@
         <v>7</v>
       </c>
       <c r="E53">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="F53">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G53">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I53" s="5">
         <v>1</v>
@@ -2872,13 +2524,13 @@
         <v>7</v>
       </c>
       <c r="E54">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="G54">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I54" s="5">
         <v>1</v>
@@ -2904,16 +2556,16 @@
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="F55">
+        <v>90</v>
+      </c>
+      <c r="G55">
         <v>80</v>
-      </c>
-      <c r="G55">
-        <v>20</v>
       </c>
       <c r="I55" s="5">
         <v>1</v>
@@ -2942,13 +2594,13 @@
         <v>7</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F56">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G56">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I56" s="5">
         <v>1</v>
@@ -2974,16 +2626,16 @@
         <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57">
-        <v>90</v>
+        <v>4.5</v>
       </c>
       <c r="G57">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="I57" s="5">
         <v>1</v>
@@ -2999,258 +2651,84 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F58">
-        <v>90</v>
-      </c>
-      <c r="G58">
-        <v>90</v>
-      </c>
-      <c r="I58" s="5">
-        <v>1</v>
-      </c>
-      <c r="J58" s="5">
-        <v>1</v>
-      </c>
-      <c r="K58" s="5">
-        <v>1</v>
-      </c>
-      <c r="L58" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>2</v>
-      </c>
-      <c r="D59" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59">
-        <v>6</v>
-      </c>
-      <c r="F59">
-        <v>4.5</v>
-      </c>
-      <c r="G59">
-        <v>30</v>
-      </c>
-      <c r="I59" s="5">
-        <v>1</v>
-      </c>
-      <c r="J59" s="5">
-        <v>1</v>
-      </c>
-      <c r="K59" s="5">
-        <v>1</v>
-      </c>
-      <c r="L59" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="I60"/>
-      <c r="J60"/>
-      <c r="K60"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A45:G46">
-    <cfRule type="expression" dxfId="50" priority="31">
-      <formula>A45="UK"</formula>
+  <conditionalFormatting sqref="A43:G57 A3:H42">
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>A3="UK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="32">
-      <formula>A45="Na"</formula>
+    <cfRule type="expression" dxfId="19" priority="4">
+      <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:H2">
-    <cfRule type="beginsWith" dxfId="48" priority="42" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="18" priority="42" operator="beginsWith" text="FI">
       <formula>LEFT(A2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="43" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H44 I6:I7 D47:G59">
-    <cfRule type="expression" dxfId="46" priority="44">
-      <formula>A3="UK"</formula>
+  <conditionalFormatting sqref="I6:I7">
+    <cfRule type="expression" dxfId="16" priority="44">
+      <formula>I6="UK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="45">
-      <formula>A3="Na"</formula>
+    <cfRule type="expression" dxfId="15" priority="45">
+      <formula>I6="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:M2">
-    <cfRule type="beginsWith" dxfId="44" priority="35" operator="beginsWith" text="UK">
+    <cfRule type="beginsWith" dxfId="14" priority="35" operator="beginsWith" text="UK">
       <formula>LEFT(A2,LEN("UK"))="UK"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="43" priority="41" operator="beginsWith" text="FU">
+    <cfRule type="beginsWith" dxfId="13" priority="41" operator="beginsWith" text="FU">
       <formula>LEFT(A2,LEN("FU"))="FU"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H44 I6:I7">
-    <cfRule type="containsText" dxfId="42" priority="46" operator="containsText" text=",">
+  <conditionalFormatting sqref="I6:I7 H3:H42">
+    <cfRule type="containsText" dxfId="12" priority="46" operator="containsText" text=",">
       <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="41" priority="47" operator="beginsWith" text="Fusion">
+    <cfRule type="beginsWith" dxfId="11" priority="47" operator="beginsWith" text="Fusion">
       <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="40" priority="48" operator="beginsWith" text="Fission">
+    <cfRule type="beginsWith" dxfId="10" priority="48" operator="beginsWith" text="Fission">
       <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="49">
+    <cfRule type="expression" dxfId="9" priority="49">
       <formula>H3="Missing Data"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="50">
+    <cfRule type="expression" dxfId="8" priority="50">
       <formula>H3="Death"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="51">
+    <cfRule type="expression" dxfId="7" priority="51">
       <formula>H3="Shrinkage"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="52">
+    <cfRule type="expression" dxfId="6" priority="52">
       <formula>H3="Growth"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="53">
+    <cfRule type="expression" dxfId="5" priority="53">
       <formula>H3="Recruitment"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="beginsWith" dxfId="34" priority="36" operator="beginsWith" text="FI">
+    <cfRule type="beginsWith" dxfId="4" priority="36" operator="beginsWith" text="FI">
       <formula>LEFT(I2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="37" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="3" priority="37" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",I2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="32" priority="38" operator="beginsWith" text="R">
+    <cfRule type="beginsWith" dxfId="2" priority="38" operator="beginsWith" text="R">
       <formula>LEFT(I2,LEN("R"))="R"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="39" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="1" priority="39" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="40" operator="containsText" text="D">
+    <cfRule type="containsText" dxfId="0" priority="40" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",I2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47:C47">
-    <cfRule type="expression" dxfId="29" priority="29">
-      <formula>A47="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="30">
-      <formula>A47="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A48:C48">
-    <cfRule type="expression" dxfId="27" priority="27">
-      <formula>A48="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="28">
-      <formula>A48="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49:C49">
-    <cfRule type="expression" dxfId="25" priority="25">
-      <formula>A49="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="26">
-      <formula>A49="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A50:C50">
-    <cfRule type="expression" dxfId="21" priority="21">
-      <formula>A50="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="22">
-      <formula>A50="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A51:C51">
-    <cfRule type="expression" dxfId="19" priority="19">
-      <formula>A51="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="20">
-      <formula>A51="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A52:C52">
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>A52="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>A52="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A53:C53">
-    <cfRule type="expression" dxfId="15" priority="15">
-      <formula>A53="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="16">
-      <formula>A53="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A54:C54">
-    <cfRule type="expression" dxfId="13" priority="13">
-      <formula>A54="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="14">
-      <formula>A54="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55:C55">
-    <cfRule type="expression" dxfId="11" priority="11">
-      <formula>A55="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="12">
-      <formula>A55="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56:C56">
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>A56="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
-      <formula>A56="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57:C57">
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>A57="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>A57="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58:C58">
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>A58="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>A58="Na"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59:C59">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>A59="UK"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>A59="Na"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
